--- a/chatbot-server/eval_scores.xlsx
+++ b/chatbot-server/eval_scores.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>question</t>
   </si>
@@ -157,90 +157,85 @@
     <t>Tentu saja. Anda tidak perlu khawatir, karena tim kami siap membantu Anda di setiap langkahnya, mulai dari awal proses hingga serah terima kunci.</t>
   </si>
   <si>
-    <t>Nama Pengembang yang dimaksudkan adalah PT Bumi Nirwana Estate. Entitas Legal Proyeknya yaitu PT Margojoyo Anugrah Persada.</t>
-  </si>
-  <si>
-    <t>Lokasi utama proyek perumahan yang saya kembangkan di Lumajang adalah Desa Klampokarum, Tekung, Lumajang.</t>
-  </si>
-  <si>
-    <t>Maaf, saya tidak dapat menemukan informasi yang Anda cari.</t>
-  </si>
-  <si>
-    <t>Harga Rumah Subsidi Tipe 1 di Margojoyo adalah Rp 166.000.000. Jika Anda ingin mendapatkan informasi lebih lanjut tentang promo dan skema pembayaran, dapat diberikan kontak pribadi langsung dari vendor atau penjual.</t>
-  </si>
-  <si>
-    <t>Simulasi angsuran KPR rumah subsidi (Margojoyo) dengan tenor 15 tahun sebanyak Rp 1.299.000 per bulan. Anda bisa mengetahui informasi lebih lanjut mengenai proses dan persyaratan melalui situs Resiko KPR Margojoyo, atau hubungi langsung kantor pemasaran atau tim layanan pelanggan untuk mendapatkan informasi yang lebih detail.</t>
-  </si>
-  <si>
-    <t>Untuk mengetahui semua informasi yang dibutuhkan tentang spesifikasi rumah subsidi Tipe 30/72 di Margojoyo, silakan hubungi konsumen service kami atau lihat website mereka. Namun, berdasarkan konteks dan informasi yang ada, informasi tertentu tidak lengkap dalam situasi ini. Saya akan meminta permohonan untuk menghubungi pihak yang bertanggung jawab (seperti pemasok atau penjual rumah subsidi) agar mendapatkan detail spesifikasi lebih lanjut dan akurat.</t>
-  </si>
-  <si>
-    <t>Maaf, saya tidak dapat menemukan informasi yang Anda cari tentang properti lain di The Margojoyo Residence. Mohon berikan lebih banyak detail atau konteks untuk membantu pertanyaan Anda.</t>
-  </si>
-  <si>
-    <t>Maaf, saya tidak dapat menemukan informasi yang Anda cari. Bisa dikatakan bahwa informasi tentang Solusi perumahan untuk milenial dengan gaji UMR dan kesulitan menabung untuk DP adalah informasi lama atau tidak ada solusi spesifik tersedia saat ini. Sebagai alternatif, mungkin bisa dicoba pertimbangkan membeli perumahan di area Sumberejo yang terletak di Desa Sumberejo, Sukodono, Lumajang. Dalam hal tersebut, anda akan mendapatkan fasilitas dan promosi lainnya yang menarik termasuk tanpa DP (DP 0%) dan gratis semua biaya.</t>
-  </si>
-  <si>
-    <t>Harga rumah di Bumi Nirwana Sumberejo adalah Rp 166.000.000. Untuk informasi lebih lanjut, silakan hubungi kami atau kunjungi situs web resmi kami untuk mendapatkan lebih banyak detail.</t>
-  </si>
-  <si>
-    <t>Rumah di Bumi Nirwana Sumberejo memiliki Ruang Keluarga (3) dan Komoditas Unggulan (Kolam Renang Pribadi).</t>
-  </si>
-  <si>
-    <t>Konsep utama dari perumahan The Royal Avenue adalah sebuah hunian mewah 2 lantai dengan desain modern dan elegan. Ini membantu mengingatkan tentang keindahan dan kualitas tinggi properti yang ditawarkan.</t>
-  </si>
-  <si>
-    <t>Kasih informasi tentang fasilitas paling unggul yang ditawarkan di setiap unit The Royal Avenue, maaf saya tidak bisa menemukan data yang Anda butuhkan.</t>
-  </si>
-  <si>
-    <t>Harga satu unit rumah di The Royal Avenue adalah Rp 300.000.000.</t>
-  </si>
-  <si>
-    <t>Maaf, saya tidak dapat menemukan informasi yang Anda cari tentang "Uang Tanda Jadi (UTJ)" atau informasi mengenai bagaimana Anda bisa mendapatkan kembali dana yang telah dikontraskan.</t>
-  </si>
-  <si>
-    <t>Biaya yang sudah termasuk dalam harga jual rumah Margojoyo adalah:
-- Perizinan: IMB/PBG (izin mendirikan bangunan)
-- Instalasi: Listrik 
-- Sumber Air: Sumur pasak
-Sementara itu, untuk Rumah Subsidi di Margojoyo, yang sudah termasuk dalam harga jualnya adalah:
-1. LUAS BANGUNAN = 30 m²
-2. LUAS TANAH = 72 m²
-3. Jumlah KAMAR TIDUR = 2
-4. Jumlah KAMAR MANDI = 1
-5. CARPOUT: TERSedia
-6. DAMPAK: Tersedia
-7. AREA TAMAN: TERSedia
-8. DAYA LISTRIK: 900 Watt
-9. Sumber Air: Sumur Bor
-Dalam hal ini, setiap rumah subsidi memiliki spesifikasi unik berdasarkan luas bangunan yang berbeda-beda, namun umumnya termasuk sebagai fitur utama dalam harga jualnya.
-Untuk Rumah Subsidi di Sumberejo:
-1. Tipe 1: Rumah Subsidi Tipe 30/72
-2. Tipe 2: Ruko (Rumah Toko) 2 Lantai
-Harga untuk rumah subsidi di Sumberejo termasuk:
-- Tipe 1: Rp 166.000.000
-- Tipe 2: Rp 257.000.000
-Selain itu, untuk Rumah Subsidi di Sumberejo, ada promo Tanpa DP (DP 0%) dan Gratis Semua Biaya. Ini menunjukkan penawaran yang lebih lembur dibandingkan dengan Margojoyo.</t>
-  </si>
-  <si>
-    <t>Untuk mengajukan KPR (Kredit Perumahan Rumah), berikut adalah dokumen yang harus dipersiapkan:
-1. Fotocopy KTP, KK, NPWP, dan Pas Foto 
-2. Surat Nikah (jika sudah menikah)
-3. Slip Gaji 3 bulan terakhir
-4. Status Pekerjaan (Surat Keterangan Kerja)
-Untuk KPR (Kredit Perwira Sekretaris) atau Wiraswasta, tambahkan dokumen berikut:
-1. Surat Jabatan (SK Terakhir)
-2. SIUP/TDP atau SKU
-Ingat untuk memeriksa persyaratan penuh dan permintaan dokumentasi yang mungkin diperlukan oleh bank untuk persyaratan pembelian rumah. Harap dicatat bahwa informasi ini bergantung pada kredibilitas prosedur penjualan perumahan di tempat Anda berada.</t>
-  </si>
-  <si>
-    <t>Maaf, saya tidak dapat menemukan informasi yang Anda cari. Mohon berikan konteks lebih lanjutan atau jelaskan dengan sedikit lebih banyak tentang apa yang Anda maksudkan dengan "dokumen tambahan" dan bagaimana dokumen tersebut menguntungkan untuk PNS atau wiraswasta.</t>
-  </si>
-  <si>
-    <t>Saya menyarankan untuk memiliki rumah sendiri untuk meminimalkan stres dan ketidakstabilan. Solusinya adalah perumahan Bumi Nirwana Sumberejo dengan promo tanpa DP (DP 0%). Jadi, Anda tidak perlu mabukkan waktu atau biaya sewa setiap tahun untuk mendapatkan rumah.</t>
-  </si>
-  <si>
-    <t>Maaf, saya tidak dapat menemukan informasi yang Anda cari. Namun, saya akan siap membantu Anda selama prosesnya. Silakan beri tahu saya apabila Anda membutuhkan bantuan atau penjelasan lebih lanjut.</t>
+    <t>Nama pengembang PT Bumi Nirwana Estate. Entitas legal proyek PT Margojoyo Anugrah Persada. (Based on the provided contexts)</t>
+  </si>
+  <si>
+    <t>Lokasinya di Desa Klampokarum, Tekung, dekat jalan raya, hanya 5 menit dari Alun-Alun Lumajang. Selain itu, juga ada lokasi utama lainnya di Sumberejo (Sukodono) dan Ditotrunan (pusat kota Lumajang).</t>
+  </si>
+  <si>
+    <t>Alamat kantor pemasaran adalah Jalan Achmad Yani No. 172, Lumajang.</t>
+  </si>
+  <si>
+    <t>Harga rumah subsidi di The Margojoyo Residence adalah Rp166.000.000. DP-nya adalah 1% atau Rp1.660.000, dengan Uang Tanda Jadi (UTJ) sebesar Rp1.000.000.</t>
+  </si>
+  <si>
+    <t>Rp1.299.000 per bulan.</t>
+  </si>
+  <si>
+    <t>Based on the provided contexts, here are the specifications of the subsidized house type 30/72 in Margojoyo:
+* 2 kamar tidur
+* 1 kamar mandi
+* Carport
+* Dapur
+* Taman
+* Listrik 900W
+* Sumber air: Sumur bor
+These specifications can be found in the context {"instruction": "Apa spesifikasi rumah subsidi Tipe 30/72 di Margojoyo?", "output": "2 kamar tidur, 1 kamar mandi, carport, dapur, taman, listrik 900W, sumur bor."}</t>
+  </si>
+  <si>
+    <t>Ada ruko 2 lantai dengan harga Rp250.000.000. (Context: "instruction": "Selain rumah, apakah ada properti lain di The Margojoyo Residence?", "output": "Ada ruko 2 lantai dengan harga Rp250.000.000.")</t>
+  </si>
+  <si>
+    <t>Ada! Perumahan Bumi Nirwana Sumberejo memiliki promo Tanpa DP (DP 0%), sehingga Anda tidak perlu khawatir dengan biaya DP yang besar. Selain itu, Anda juga dapat memilih angsuran yang lebih ringan dan mudah dibayarkan.</t>
+  </si>
+  <si>
+    <t>Harga rumah di Bumi Nirwana Sumberejo adalah Rp166.000.000. Promo tanpa DP (DP 0%) dan gratis semua biaya.</t>
+  </si>
+  <si>
+    <t>Berikut spesifikasi rumah di Bumi Nirwana Sumberejo:
+* 2 kamar tidur
+* 1 kamar mandi
+* Carport
+* Ruang serbaguna</t>
+  </si>
+  <si>
+    <t>Hunian mewah 2 lantai, desain modern dan elegan.</t>
+  </si>
+  <si>
+    <t>Setiap rumah memiliki kolam renang pribadi.</t>
+  </si>
+  <si>
+    <t>Rp300.000.000 dengan promo gratis semua biaya.</t>
+  </si>
+  <si>
+    <t>Uang Tanda Jadi (UTJ) adalah biaya untuk mengamankan unit pilihan Anda, sekitar Rp750.000 hingga Rp1.000.000. Menurut informasi, UTJ tidak dapat dikembalikan jika terjadi pembatalan sepihak dari konsumen.</t>
+  </si>
+  <si>
+    <t>DP dapat dikembalikan jika pengajuan KPR ditolak oleh bank karena masalah BI Checking.</t>
+  </si>
+  <si>
+    <t>IMB/PBG, listrik, sumur pasak.</t>
+  </si>
+  <si>
+    <t>Dokumen-dokumen yang umumnya diperlukan untuk mengajukan KPR adalah:
+* Fotokopi KTP
+* KK (Kartu Keluarga)
+* NPWP (Nomer Pokok Wajib Pajak)
+* Pas Foto
+* Surat Nikah (jika sudah menikah)
+* Slip Gaji 3 bulan terakhir
+* Surat Keterangan Kerja
+Namun, dokumen tambahan yang diperlukan untuk PNS adalah SK Terakhir, sedangkan untuk Wiraswasta adalah SIUP/TDP atau SKU.</t>
+  </si>
+  <si>
+    <t>Jika Anda seorang PNS, maka Anda wajib melampirkan SK Terakhir.
+Jika Anda seorang wiraswasta, maka Anda wajib melampirkan SIUP/TDP atau SKU.</t>
+  </si>
+  <si>
+    <t>Bisa memilih rumah subsidi dengan cicilan ringan, sering lebih murah dari biaya sewa.</t>
+  </si>
+  <si>
+    <t>Jaminan! Tim kami siap membantu Anda di setiap langkahnya, dari awal hingga serah terima kunci. Proses KPR dapat terasa rumit, tapi dengan bantuan kami, Anda tidak perlu khawatir lagi. Kami akan membantu Anda dalam mengajukan KPR dan menghadapi semua tantangan yang mungkin timbul.</t>
   </si>
 </sst>
 </file>
@@ -603,7 +598,7 @@
   <cols>
     <col min="1" max="1" width="112.7109375" customWidth="1"/>
     <col min="2" max="2" width="196.7109375" customWidth="1"/>
-    <col min="3" max="3" width="1033.7109375" customWidth="1"/>
+    <col min="3" max="3" width="423.7109375" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" customWidth="1"/>
@@ -644,16 +639,16 @@
         <v>47</v>
       </c>
       <c r="D2">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="E2">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="F2">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="G2">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -667,16 +662,16 @@
         <v>48</v>
       </c>
       <c r="D3">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="E3">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="F3">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G3">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -690,16 +685,16 @@
         <v>49</v>
       </c>
       <c r="D4">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="E4">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="F4">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="G4">
-        <v>0.07000000000000001</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -713,16 +708,16 @@
         <v>50</v>
       </c>
       <c r="D5">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="E5">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="F5">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="G5">
-        <v>0.39</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -736,16 +731,16 @@
         <v>51</v>
       </c>
       <c r="D6">
-        <v>0.68</v>
+        <v>0.85</v>
       </c>
       <c r="E6">
-        <v>0.91</v>
+        <v>0.63</v>
       </c>
       <c r="F6">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="G6">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -759,16 +754,16 @@
         <v>52</v>
       </c>
       <c r="D7">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="E7">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="F7">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="G7">
-        <v>0.02</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -782,16 +777,16 @@
         <v>53</v>
       </c>
       <c r="D8">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="E8">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="F8">
-        <v>0.68</v>
+        <v>0.79</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -805,16 +800,16 @@
         <v>54</v>
       </c>
       <c r="D9">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="E9">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="F9">
-        <v>0.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G9">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -828,16 +823,16 @@
         <v>55</v>
       </c>
       <c r="D10">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="E10">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="F10">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="G10">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -851,16 +846,16 @@
         <v>56</v>
       </c>
       <c r="D11">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="E11">
         <v>0.84</v>
       </c>
       <c r="F11">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="G11">
-        <v>0.44</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -874,16 +869,16 @@
         <v>57</v>
       </c>
       <c r="D12">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="E12">
-        <v>0.88</v>
+        <v>0.58</v>
       </c>
       <c r="F12">
-        <v>0.84</v>
+        <v>0.68</v>
       </c>
       <c r="G12">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -897,16 +892,16 @@
         <v>58</v>
       </c>
       <c r="D13">
-        <v>0.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E13">
-        <v>0.89</v>
+        <v>0.65</v>
       </c>
       <c r="F13">
-        <v>0.8100000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="G13">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -920,16 +915,16 @@
         <v>59</v>
       </c>
       <c r="D14">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="E14">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
       <c r="F14">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G14">
-        <v>0.44</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -943,16 +938,16 @@
         <v>60</v>
       </c>
       <c r="D15">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="E15">
-        <v>0.74</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F15">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="G15">
-        <v>0.09</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -963,19 +958,19 @@
         <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16">
-        <v>0.72</v>
+        <v>0.96</v>
       </c>
       <c r="E16">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="F16">
-        <v>0.68</v>
+        <v>0.96</v>
       </c>
       <c r="G16">
-        <v>0.15</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -986,19 +981,19 @@
         <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D17">
-        <v>0.55</v>
+        <v>0.88</v>
       </c>
       <c r="E17">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="F17">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="G17">
-        <v>0.12</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1009,19 +1004,19 @@
         <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D18">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="E18">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="F18">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="G18">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1032,19 +1027,19 @@
         <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D19">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="E19">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="F19">
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
       <c r="G19">
-        <v>0.12</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1055,19 +1050,19 @@
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D20">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="E20">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="F20">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="G20">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1078,19 +1073,19 @@
         <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D21">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="E21">
-        <v>0.74</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F21">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="G21">
-        <v>0.15</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
